--- a/data/stx_xlsx/BMAX.ST.xlsx
+++ b/data/stx_xlsx/BMAX.ST.xlsx
@@ -9601,7 +9601,9 @@
       <c r="L43" s="21">
         <v>25.12</v>
       </c>
-      <c r="M43" s="20"/>
+      <c r="M43" s="21">
+        <v>29.62</v>
+      </c>
       <c r="N43" s="21">
         <v>23.28</v>
       </c>

--- a/data/stx_xlsx/BMAX.ST.xlsx
+++ b/data/stx_xlsx/BMAX.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="395">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -793,6 +793,9 @@
   </si>
   <si>
     <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Borrowing from credit institutions (Do not use)</t>
   </si>
   <si>
     <t>Lease liabilities</t>
@@ -11614,9 +11617,15 @@
       <c r="A95" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="B95" s="20"/>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
+      <c r="B95" s="15">
+        <v>400.21</v>
+      </c>
+      <c r="C95" s="15">
+        <v>646.67</v>
+      </c>
+      <c r="D95" s="15">
+        <v>964.48</v>
+      </c>
       <c r="E95" s="15">
         <v>771.84</v>
       </c>
@@ -11641,15 +11650,27 @@
       <c r="L95" s="15">
         <v>209.31</v>
       </c>
-      <c r="M95" s="20"/>
+      <c r="M95" s="15">
+        <v>460.56</v>
+      </c>
       <c r="N95" s="21">
         <v>94.25</v>
       </c>
-      <c r="O95" s="20"/>
-      <c r="P95" s="20"/>
-      <c r="Q95" s="20"/>
-      <c r="R95" s="20"/>
-      <c r="S95" s="20"/>
+      <c r="O95" s="15">
+        <v>413.89</v>
+      </c>
+      <c r="P95" s="15">
+        <v>298.49</v>
+      </c>
+      <c r="Q95" s="15">
+        <v>208.24</v>
+      </c>
+      <c r="R95" s="21">
+        <v>57.71</v>
+      </c>
+      <c r="S95" s="21">
+        <v>95.0</v>
+      </c>
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
@@ -12529,8 +12550,8 @@
       </c>
     </row>
     <row r="117" ht="15.0" customHeight="1">
-      <c r="A117" s="14" t="s">
-        <v>239</v>
+      <c r="A117" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -12577,7 +12598,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B118" s="15">
         <v>1358.09</v>
@@ -12616,7 +12637,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B119" s="15">
         <v>106.07</v>
@@ -12675,7 +12696,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -12710,7 +12731,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -12739,7 +12760,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20">
@@ -12782,7 +12803,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -12815,7 +12836,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B124" s="17">
         <v>1464.15</v>
@@ -12874,7 +12895,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B125" s="17">
         <v>3221.35</v>
@@ -12933,7 +12954,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="15">
@@ -12976,7 +12997,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="21">
@@ -13031,7 +13052,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="15">
@@ -13086,7 +13107,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="21">
@@ -13168,7 +13189,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="21">
@@ -13207,7 +13228,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B132" s="17">
         <v>2751.16</v>
@@ -13266,7 +13287,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B133" s="17">
         <v>2751.16</v>
@@ -13325,7 +13346,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="21">
@@ -13360,7 +13381,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B135" s="17">
         <v>5972.52</v>
@@ -13419,7 +13440,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B136" s="21">
         <v>58.63</v>
@@ -13478,7 +13499,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B137" s="21">
         <v>58.63</v>
@@ -13537,7 +13558,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B138" s="20">
         <v>0.0</v>
@@ -13596,7 +13617,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -13625,7 +13646,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -13652,7 +13673,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="15">
@@ -13701,7 +13722,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="15">
@@ -13734,7 +13755,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="15">
@@ -13783,7 +13804,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="15">
@@ -13830,7 +13851,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -13875,7 +13896,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B146" s="21">
         <v>58.63</v>
@@ -13934,7 +13955,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B147" s="21">
         <v>58.63</v>
@@ -13993,7 +14014,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B148" s="21">
         <v>1.0</v>
@@ -14052,7 +14073,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B149" s="20">
         <v>0.0</v>
@@ -14982,7 +15003,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15316,58 +15337,58 @@
         <v>40</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15431,7 +15452,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15513,7 +15534,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B20" s="15">
         <v>699.05</v>
@@ -15548,7 +15569,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -15581,7 +15602,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B22" s="18">
         <v>-83.67</v>
@@ -15606,7 +15627,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B23" s="15">
         <v>955.36</v>
@@ -15718,7 +15739,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -15765,7 +15786,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B26" s="21">
         <v>80.5</v>
@@ -15824,7 +15845,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="21">
@@ -15881,7 +15902,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="19">
@@ -15938,7 +15959,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" s="18">
         <v>-65.67</v>
@@ -15997,7 +16018,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -16022,7 +16043,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B31" s="18">
         <v>-36.01</v>
@@ -16081,7 +16102,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" s="21">
         <v>11.65</v>
@@ -16140,7 +16161,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" s="18">
         <v>-74.14</v>
@@ -16199,7 +16220,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -16249,7 +16270,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" s="21">
         <v>1.06</v>
@@ -16288,7 +16309,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" s="17">
         <v>856.86</v>
@@ -16347,7 +16368,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" s="18">
         <v>-27.54</v>
@@ -16404,7 +16425,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B39" s="18">
         <v>-60.37</v>
@@ -16463,7 +16484,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -16510,7 +16531,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" s="21">
         <v>3.18</v>
@@ -16547,7 +16568,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -16574,7 +16595,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -16619,7 +16640,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -16646,7 +16667,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -16687,7 +16708,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B46" s="20">
         <v>0.0</v>
@@ -16720,7 +16741,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -16749,7 +16770,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -16819,7 +16840,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -16848,7 +16869,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -16875,7 +16896,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B52" s="21">
         <v>1.06</v>
@@ -16906,7 +16927,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B53" s="22">
         <v>-83.67</v>
@@ -16965,7 +16986,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B54" s="19">
         <v>-278.56</v>
@@ -17020,7 +17041,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B55" s="19">
         <v>-450.14</v>
@@ -17057,7 +17078,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -17108,7 +17129,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -17147,7 +17168,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B58" s="21">
         <v>2.12</v>
@@ -17190,7 +17211,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B59" s="18">
         <v>-46.6</v>
@@ -17241,7 +17262,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -17278,7 +17299,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B61" s="18">
         <v>-1.06</v>
@@ -17317,7 +17338,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B62" s="23">
         <v>-774.25</v>
@@ -17376,7 +17397,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B63" s="21">
         <v>12.03</v>
@@ -17435,7 +17456,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B64" s="21">
         <v>12.03</v>
@@ -17494,7 +17515,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B65" s="21">
         <v>1.06</v>
@@ -17527,7 +17548,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B66" s="20">
         <v>0.0</v>
@@ -17560,7 +17581,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -17593,7 +17614,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B68" s="25">
         <v>0.0</v>
@@ -17652,7 +17673,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -17677,7 +17698,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -17708,7 +17729,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -18686,7 +18707,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18835,7 +18856,7 @@
         <v>35</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -19135,7 +19156,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19212,12 +19233,12 @@
         <v>62</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -19240,7 +19261,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B21" s="30">
         <v>5242.71</v>
@@ -19293,7 +19314,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B22" s="30">
         <v>5805.52</v>
@@ -19338,7 +19359,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -19361,7 +19382,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B24" s="30">
         <v>2707.43</v>
@@ -19414,7 +19435,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B25" s="30">
         <v>3364.41</v>
@@ -19459,7 +19480,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -19482,7 +19503,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B27" s="32">
         <v>46.18</v>
@@ -19535,7 +19556,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B28" s="32">
         <v>56.22</v>
@@ -19580,7 +19601,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -19603,7 +19624,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B30" s="33">
         <v>29.62</v>
@@ -19656,7 +19677,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B31" s="33">
         <v>20.22</v>
@@ -19701,7 +19722,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -19724,7 +19745,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B33" s="33">
         <v>0.78</v>
@@ -19777,7 +19798,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B34" s="33">
         <v>1.86</v>
@@ -19822,7 +19843,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B35" s="33">
         <v>1.11</v>
@@ -19875,7 +19896,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B36" s="33">
         <v>2.65</v>
@@ -19920,7 +19941,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -19943,7 +19964,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B38" s="32">
         <v>1.1</v>
@@ -19996,7 +20017,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" s="32">
         <v>1.42</v>
@@ -20041,7 +20062,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="27" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
@@ -20064,7 +20085,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="29" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B41" s="32">
         <v>16.88</v>
@@ -20091,7 +20112,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B42" s="30">
         <v>761.52</v>
@@ -20116,7 +20137,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
@@ -20139,7 +20160,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B44" s="32">
         <v>0.44</v>
@@ -20192,7 +20213,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" s="32">
         <v>0.48</v>
@@ -20237,7 +20258,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="27" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B46" s="28"/>
       <c r="C46" s="28"/>
@@ -20260,7 +20281,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" s="32">
         <v>3.38</v>
@@ -20313,7 +20334,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B48" s="32">
         <v>4.95</v>
@@ -20358,7 +20379,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="27" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B49" s="28"/>
       <c r="C49" s="28"/>
@@ -20381,7 +20402,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B50" s="32">
         <v>3.55</v>
@@ -20434,7 +20455,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" s="32">
         <v>3.65</v>
@@ -20479,7 +20500,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
@@ -20502,7 +20523,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B53" s="32">
         <v>39.9</v>
@@ -20555,7 +20576,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B54" s="32">
         <v>10.93</v>
@@ -20600,7 +20621,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
@@ -20623,7 +20644,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="29" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B56" s="32">
         <v>39.3</v>
@@ -20676,7 +20697,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B57" s="32">
         <v>1.42</v>
@@ -20721,7 +20742,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B58" s="28"/>
       <c r="C58" s="28"/>
@@ -20744,7 +20765,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" s="32">
         <v>0.26</v>
@@ -20797,7 +20818,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B60" s="34">
         <v>-0.81</v>
@@ -20842,7 +20863,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B61" s="28"/>
       <c r="C61" s="28"/>
@@ -20865,7 +20886,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B62" s="32">
         <v>0.85</v>
@@ -20918,7 +20939,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B63" s="32">
         <v>0.84</v>
@@ -20963,7 +20984,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
@@ -20986,7 +21007,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="29" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B65" s="32">
         <v>5.91</v>
@@ -21039,7 +21060,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B66" s="32">
         <v>5.04</v>
@@ -21084,7 +21105,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="27" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -21107,7 +21128,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B68" s="32">
         <v>5.93</v>
@@ -21160,7 +21181,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="29" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" s="32">
         <v>6.74</v>
@@ -21205,7 +21226,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="27" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B70" s="28"/>
       <c r="C70" s="28"/>
@@ -21228,7 +21249,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="29" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B71" s="32">
         <v>6.54</v>
@@ -21281,7 +21302,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="29" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" s="32">
         <v>8.55</v>
